--- a/capabilities/pipeline-projection/model.xlsx
+++ b/capabilities/pipeline-projection/model.xlsx
@@ -698,11 +698,11 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>100</v>
+        <v>20000</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>PLACEHOLDER. Illustrative only — replace with your own assumption or a real hiring count.</t>
+          <t>BLS Occupational Outlook Handbook, Graphic Designers (2024-2034 projections): ~20,000 average annual openings. Note: BLS "openings" bundles growth openings with replacement openings (anyone leaving the occupation, any career stage), not specifically junior hires.</t>
         </is>
       </c>
     </row>
@@ -713,11 +713,11 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.7</v>
+        <v>0.855</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>PLACEHOLDER. Share of baseline hiring under the Depressed scenario, from Base_Year+1 onward.</t>
+          <t>Derived from Brynjolfsson, Chandar &amp; Chen (revised Aug 2026), Table 1 Panel A: AI-exposure Quintile 4 (Graphic Designers' quintile per Table A.5) shows a -14.5% employment coefficient for ages 22-25 vs. Quintile 1, in the paper's primary 2018-balanced sample. 0.855 = 1 - 0.145. Caveat: this is a regression coefficient on employment stock, not a literal hiring-rate reduction, though the paper's Fact 4 attributes the decline to reduced hiring rather than increased separations.</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>PLACEHOLDER. Share of a hired cohort that survives to become mid-level after N years (distinct from attrition after that point).</t>
+          <t>Jennifer's professional judgment: share of a hired cohort that survives to become mid-level after N years (distinct from attrition after that point). No occupation-specific source found.</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>PLACEHOLDER. Applied after each year's new cohort joins the mid-level stock (per the agreed ordering).</t>
+          <t>Jennifer's professional judgment: annual attrition rate applied to the mid-level stock, after each year's new cohort joins (per the agreed ordering). No occupation-specific source found.</t>
         </is>
       </c>
     </row>

--- a/capabilities/pipeline-projection/model.xlsx
+++ b/capabilities/pipeline-projection/model.xlsx
@@ -803,11 +803,11 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>500</v>
+        <v>98685</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>PLACEHOLDER. Actual or assumed mid-level headcount in Base_Year; same across all scenarios since none have diverged yet.</t>
+          <t>IPUMS CPS Basic Monthly, OCC 2634 (Graphic Designers), employed (EMPSTAT 10/12), age 26-35, 2022. Weighted headcount averaged across the 12 monthly samples (range 77,280-117,161; unweighted N=350 across the year, ~23-68/month). See prompt-log.md 2026-10-09 entry.</t>
         </is>
       </c>
     </row>
